--- a/artfynd/A 22404-2024 artfynd.xlsx
+++ b/artfynd/A 22404-2024 artfynd.xlsx
@@ -1557,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118257836</v>
+        <v>118257900</v>
       </c>
       <c r="B9" t="n">
-        <v>97869</v>
+        <v>97821</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724283</v>
+        <v>724228</v>
       </c>
       <c r="R9" t="n">
-        <v>6377857</v>
+        <v>6377893</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,11 +1633,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118257900</v>
+        <v>118257836</v>
       </c>
       <c r="B10" t="n">
-        <v>97821</v>
+        <v>97869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219797</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1704,13 +1699,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724228</v>
+        <v>724283</v>
       </c>
       <c r="R10" t="n">
-        <v>6377893</v>
+        <v>6377857</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1740,6 +1735,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 22404-2024 artfynd.xlsx
+++ b/artfynd/A 22404-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6632779</v>
+        <v>179982</v>
       </c>
       <c r="B2" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>249228</v>
+        <v>442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724111.6848534431</v>
+        <v>724093</v>
       </c>
       <c r="R2" t="n">
-        <v>6377789.132106885</v>
+        <v>6377873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2012-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,62 +786,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1342328</v>
+        <v>96502492</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kräklingbo, gurpe, Gtl</t>
+          <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724098.8085539751</v>
+        <v>724428</v>
       </c>
       <c r="R3" t="n">
-        <v>6377856.292751431</v>
+        <v>6378085</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,68 +887,62 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>179982</v>
+        <v>1161785</v>
       </c>
       <c r="B4" t="n">
-        <v>85172</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>442</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -976,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724093.0189460551</v>
+        <v>724099</v>
       </c>
       <c r="R4" t="n">
-        <v>6377873.210398798</v>
+        <v>6377856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +984,9 @@
           <t>2012-10-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-10-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,42 +1018,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6624130</v>
+        <v>96502499</v>
       </c>
       <c r="B5" t="n">
-        <v>85138</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248952</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1096,19 +1056,20 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kräklingbo, gurpe, Gtl</t>
+          <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724111.6848534431</v>
+        <v>724429</v>
       </c>
       <c r="R5" t="n">
-        <v>6377789.132106885</v>
+        <v>6378080</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,36 +1119,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1161785</v>
+        <v>1342328</v>
       </c>
       <c r="B6" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,31 +1150,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1228,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724098.8085539751</v>
+        <v>724099</v>
       </c>
       <c r="R6" t="n">
-        <v>6377856.292751431</v>
+        <v>6377856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1216,9 @@
           <t>2012-10-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-10-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,63 +1250,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96502492</v>
+        <v>118257900</v>
       </c>
       <c r="B7" t="n">
-        <v>89175</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2015</v>
+        <v>219797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bendes, Anga, Gtl</t>
+          <t>Käldvät, Käldvät, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724428.3506640076</v>
+        <v>724228</v>
       </c>
       <c r="R7" t="n">
-        <v>6378085.075139595</v>
+        <v>6377893</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,22 +1315,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,31 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96502499</v>
+        <v>118257836</v>
       </c>
       <c r="B8" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,44 +1358,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bendes, Anga, Gtl</t>
+          <t>Käldvät, Käldvät, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724428.6470632752</v>
+        <v>724283</v>
       </c>
       <c r="R8" t="n">
-        <v>6378079.705252558</v>
+        <v>6377857</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1511,22 +1412,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,31 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118257900</v>
+        <v>118257826</v>
       </c>
       <c r="B9" t="n">
-        <v>97821</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,37 +1460,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219797</v>
+        <v>222118</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Käldvät (Käldvät), Gtl</t>
+          <t>Käldvät, Käldvät, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724228</v>
+        <v>724281</v>
       </c>
       <c r="R9" t="n">
-        <v>6377893</v>
+        <v>6377865</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1659,53 +1546,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118257836</v>
+        <v>6624130</v>
       </c>
       <c r="B10" t="n">
-        <v>97869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>248952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Käldvät (Käldvät), Gtl</t>
+          <t>Kräklingbo, gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724283</v>
+        <v>724112</v>
       </c>
       <c r="R10" t="n">
-        <v>6377857</v>
+        <v>6377789</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,17 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,69 +1636,78 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118257826</v>
+        <v>6632779</v>
       </c>
       <c r="B11" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222118</v>
+        <v>249228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Käldvät (Käldvät), Gtl</t>
+          <t>Kräklingbo, gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724281</v>
+        <v>724112</v>
       </c>
       <c r="R11" t="n">
-        <v>6377865</v>
+        <v>6377789</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,12 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,16 +1747,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 22404-2024 artfynd.xlsx
+++ b/artfynd/A 22404-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96502492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1161785</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96502499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1342328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118257900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118257836</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118257826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1765,8 +1815,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6632779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>